--- a/docs/export-templates/AI问书_全域订单数据导出.xlsx
+++ b/docs/export-templates/AI问书_全域订单数据导出.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="120">
   <si>
     <t>平台全域订单</t>
   </si>
@@ -58,30 +58,72 @@
     <t>兑换时间</t>
   </si>
   <si>
+    <t>OD20260722100215</t>
+  </si>
+  <si>
+    <t>XX 出版社</t>
+  </si>
+  <si>
+    <t>会员</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>¥19.9</t>
+  </si>
+  <si>
+    <t>微信支付</t>
+  </si>
+  <si>
+    <t>待支付</t>
+  </si>
+  <si>
+    <t>未退款</t>
+  </si>
+  <si>
+    <t>13800138888</t>
+  </si>
+  <si>
+    <t>2026-07-22 10:02:15</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>OD20260721143050</t>
+  </si>
+  <si>
+    <t>永享</t>
+  </si>
+  <si>
+    <t>心血管分册</t>
+  </si>
+  <si>
+    <t>¥9.9</t>
+  </si>
+  <si>
+    <t>已失效</t>
+  </si>
+  <si>
+    <t>wx_abc</t>
+  </si>
+  <si>
+    <t>2026-07-21 14:30:50</t>
+  </si>
+  <si>
     <t>OD20260530173044</t>
   </si>
   <si>
     <t>YY 教育</t>
   </si>
   <si>
-    <t>会员</t>
-  </si>
-  <si>
-    <t>—</t>
-  </si>
-  <si>
     <t>¥198</t>
   </si>
   <si>
-    <t>微信支付</t>
-  </si>
-  <si>
     <t>已支付</t>
   </si>
   <si>
-    <t>未退款</t>
-  </si>
-  <si>
     <t>15000133322</t>
   </si>
   <si>
@@ -94,21 +136,6 @@
     <t>OD20260530152133</t>
   </si>
   <si>
-    <t>XX 出版社</t>
-  </si>
-  <si>
-    <t>永享</t>
-  </si>
-  <si>
-    <t>心血管分册</t>
-  </si>
-  <si>
-    <t>¥9.9</t>
-  </si>
-  <si>
-    <t>wx_abc</t>
-  </si>
-  <si>
     <t>2026-05-30 15:21:20</t>
   </si>
   <si>
@@ -116,12 +143,6 @@
   </si>
   <si>
     <t>OD20260530140208</t>
-  </si>
-  <si>
-    <t>¥19.9</t>
-  </si>
-  <si>
-    <t>13800138888</t>
   </si>
   <si>
     <t>2026-05-30 14:01:50</t>
@@ -816,7 +837,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L24"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -959,22 +980,22 @@
         <v>26</v>
       </c>
       <c r="B6" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="D6" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="E6" s="7" t="s">
         <v>29</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>30</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>20</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="H6" s="7" t="s">
         <v>22</v>
@@ -986,7 +1007,7 @@
         <v>32</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="L6" s="7" t="s">
         <v>18</v>
@@ -994,10 +1015,10 @@
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>34</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>27</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>17</v>
@@ -1012,19 +1033,19 @@
         <v>20</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>22</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L7" s="5" t="s">
         <v>18</v>
@@ -1032,37 +1053,37 @@
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>16</v>
       </c>
       <c r="C8" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="7" t="s">
-        <v>40</v>
-      </c>
       <c r="E8" s="7" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>20</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="H8" s="7" t="s">
         <v>22</v>
       </c>
       <c r="I8" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="K8" s="7" t="s">
         <v>42</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>44</v>
       </c>
       <c r="L8" s="7" t="s">
         <v>18</v>
@@ -1070,75 +1091,75 @@
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="K9" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="I9" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="J9" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="K9" s="5" t="s">
-        <v>18</v>
-      </c>
       <c r="L9" s="5" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B10" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="7" t="s">
-        <v>28</v>
-      </c>
       <c r="D10" s="7" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>20</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="H10" s="7" t="s">
         <v>22</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="L10" s="7" t="s">
         <v>18</v>
@@ -1146,75 +1167,75 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I11" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="J11" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="L11" s="5" t="s">
         <v>58</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="I11" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="J11" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="K11" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="L11" s="5" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B12" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="7" t="s">
-        <v>17</v>
-      </c>
       <c r="D12" s="7" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>20</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="H12" s="7" t="s">
         <v>22</v>
       </c>
       <c r="I12" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J12" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="K12" s="7" t="s">
         <v>63</v>
-      </c>
-      <c r="J12" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="K12" s="7" t="s">
-        <v>65</v>
       </c>
       <c r="L12" s="7" t="s">
         <v>18</v>
@@ -1222,40 +1243,40 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I13" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="I13" s="5" t="s">
+      <c r="J13" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="J13" s="5" t="s">
-        <v>18</v>
-      </c>
       <c r="K13" s="5" t="s">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="L13" s="5" t="s">
-        <v>68</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -1263,22 +1284,22 @@
         <v>69</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>18</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="H14" s="7" t="s">
         <v>22</v>
@@ -1287,51 +1308,51 @@
         <v>70</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>18</v>
+        <v>71</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>18</v>
+        <v>72</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>71</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>18</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>21</v>
+        <v>56</v>
       </c>
       <c r="H15" s="5" t="s">
         <v>22</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="K15" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="L15" s="5" t="s">
         <v>75</v>
-      </c>
-      <c r="L15" s="5" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -1339,72 +1360,72 @@
         <v>76</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="D16" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I16" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="E16" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G16" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="H16" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="I16" s="7" t="s">
+      <c r="J16" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="K16" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L16" s="7" t="s">
         <v>78</v>
-      </c>
-      <c r="J16" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="K16" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="L16" s="7" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>82</v>
+        <v>18</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="H17" s="5" t="s">
         <v>22</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="K17" s="5" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="L17" s="5" t="s">
         <v>18</v>
@@ -1412,37 +1433,37 @@
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B18" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C18" s="7" t="s">
-        <v>17</v>
-      </c>
       <c r="D18" s="7" t="s">
-        <v>18</v>
+        <v>84</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="F18" s="7" t="s">
         <v>20</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="H18" s="7" t="s">
         <v>22</v>
       </c>
       <c r="I18" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="J18" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="K18" s="7" t="s">
         <v>87</v>
-      </c>
-      <c r="J18" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="K18" s="7" t="s">
-        <v>89</v>
       </c>
       <c r="L18" s="7" t="s">
         <v>18</v>
@@ -1450,37 +1471,37 @@
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B19" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C19" s="5" t="s">
-        <v>28</v>
-      </c>
       <c r="D19" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="E19" s="5" t="s">
         <v>29</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>35</v>
       </c>
       <c r="F19" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="H19" s="5" t="s">
         <v>22</v>
       </c>
       <c r="I19" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="J19" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="J19" s="5" t="s">
+      <c r="K19" s="5" t="s">
         <v>92</v>
-      </c>
-      <c r="K19" s="5" t="s">
-        <v>93</v>
       </c>
       <c r="L19" s="5" t="s">
         <v>18</v>
@@ -1488,10 +1509,10 @@
     </row>
     <row r="20" ht="24" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>17</v>
@@ -1500,25 +1521,25 @@
         <v>18</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="F20" s="7" t="s">
         <v>20</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="H20" s="7" t="s">
         <v>22</v>
       </c>
       <c r="I20" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="J20" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="J20" s="7" t="s">
+      <c r="K20" s="7" t="s">
         <v>96</v>
-      </c>
-      <c r="K20" s="7" t="s">
-        <v>97</v>
       </c>
       <c r="L20" s="7" t="s">
         <v>18</v>
@@ -1526,40 +1547,40 @@
     </row>
     <row r="21" ht="24" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I21" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="H21" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="I21" s="5" t="s">
+      <c r="J21" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="J21" s="5" t="s">
-        <v>18</v>
-      </c>
       <c r="K21" s="5" t="s">
-        <v>18</v>
+        <v>100</v>
       </c>
       <c r="L21" s="5" t="s">
-        <v>100</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -1567,34 +1588,34 @@
         <v>101</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>103</v>
+        <v>19</v>
       </c>
       <c r="F22" s="7" t="s">
         <v>20</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="H22" s="7" t="s">
         <v>22</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>31</v>
+        <v>102</v>
       </c>
       <c r="J22" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="K22" s="7" t="s">
         <v>104</v>
-      </c>
-      <c r="K22" s="7" t="s">
-        <v>105</v>
       </c>
       <c r="L22" s="7" t="s">
         <v>18</v>
@@ -1602,69 +1623,69 @@
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I23" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="H23" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="I23" s="5" t="s">
-        <v>73</v>
-      </c>
       <c r="J23" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K23" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="L23" s="5" t="s">
         <v>107</v>
-      </c>
-      <c r="K23" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="L23" s="5" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D24" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="B24" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>102</v>
-      </c>
       <c r="E24" s="7" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="F24" s="7" t="s">
         <v>20</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="H24" s="7" t="s">
         <v>22</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
       <c r="J24" s="7" t="s">
         <v>111</v>
@@ -1673,6 +1694,82 @@
         <v>112</v>
       </c>
       <c r="L24" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" ht="24" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I25" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="J25" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="K25" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="L25" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="26" ht="24" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I26" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="J26" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="K26" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="L26" s="7" t="s">
         <v>18</v>
       </c>
     </row>
